--- a/artfynd/A 30317-2024 artfynd.xlsx
+++ b/artfynd/A 30317-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115368874</v>
+        <v>74500689</v>
       </c>
       <c r="B2" t="n">
-        <v>83044</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>232272</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Beck) Boud.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarntorpet, Väderlanda, Sm</t>
+          <t>12 Berghem 700 m SO, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502830</v>
+        <v>502795</v>
       </c>
       <c r="R2" t="n">
-        <v>6291004</v>
+        <v>6291008</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -756,17 +736,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>1983-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fuktig sluttning med klibbal</t>
+          <t>Smålands flora 2007: KOO: 4F8a 3135. SOM: Huperzia selago. LEG: Curt Mossberg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +755,149 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>F.d.kvarntorpet-bäckutlopp</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115368874</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83044</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kvarntorpet, Väderlanda, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>502830</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6291004</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nöbbele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fuktig sluttning med klibbal</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Tomas Lundqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Tomas Lundqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30317-2024 artfynd.xlsx
+++ b/artfynd/A 30317-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>132015383</v>
       </c>
       <c r="B4" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2024 artfynd.xlsx
+++ b/artfynd/A 30317-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>132015383</v>
       </c>
       <c r="B4" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2024 artfynd.xlsx
+++ b/artfynd/A 30317-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>132015383</v>
       </c>
       <c r="B4" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2024 artfynd.xlsx
+++ b/artfynd/A 30317-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>132015383</v>
       </c>
       <c r="B4" t="n">
-        <v>97981</v>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2024 artfynd.xlsx
+++ b/artfynd/A 30317-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,44 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74500689</v>
+        <v>86920299</v>
       </c>
       <c r="B2" t="n">
-        <v>97534</v>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>12 Berghem 700 m SO, Sm</t>
+          <t>Kvarntorpet, Väderlanda, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502795</v>
+        <v>502786</v>
       </c>
       <c r="R2" t="n">
-        <v>6291008</v>
+        <v>6291033</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -736,17 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 4F8a 3135. SOM: Huperzia selago. LEG: Curt Mossberg</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -758,39 +765,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>F.d.kvarntorpet-bäckutlopp</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115368874</v>
+        <v>74500689</v>
       </c>
       <c r="B3" t="n">
-        <v>83044</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,45 +791,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>232272</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Beck) Boud.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarntorpet, Väderlanda, Sm</t>
+          <t>12 Berghem 700 m SO, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502830</v>
+        <v>502795</v>
       </c>
       <c r="R3" t="n">
-        <v>6291004</v>
+        <v>6291008</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -863,17 +841,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>1983-12-31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fuktig sluttning med klibbal</t>
+          <t>Smålands flora 2007: KOO: 4F8a 3135. SOM: Huperzia selago. LEG: Curt Mossberg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,29 +860,37 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>F.d.kvarntorpet-bäckutlopp</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>132015383</v>
       </c>
       <c r="B4" t="n">
-        <v>97983</v>
+        <v>98060</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,6 +997,120 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115368874</v>
+      </c>
+      <c r="B5" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvarntorpet, Väderlanda, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>502830</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6291004</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nöbbele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fuktig sluttning med klibbal</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30317-2024 artfynd.xlsx
+++ b/artfynd/A 30317-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86920299</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74500689</t>
         </is>
       </c>
     </row>
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132015383</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,8 +1130,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115368874</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>